--- a/Calculation Module/investment-api-performance-crosswalk.xlsx
+++ b/Calculation Module/investment-api-performance-crosswalk.xlsx
@@ -134,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -171,11 +171,55 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -222,6 +266,8 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -974,7 +1020,7 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>PERSONAL_FLOWS / INGEST_ACTIVITY_TYPE</t>
+          <t>PERSONAL_FLOWS / TRANSLATE_BROKER_WORD</t>
         </is>
       </c>
       <c r="I8" s="16" t="inlineStr">
@@ -984,7 +1030,7 @@
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>A CLOSED TRANSACTION TAXONOMY. Any broker word we do not recognise is currently guessed from the sign of the amount. On the founder's real file that produced $1,064,493 of contributions on an account where nothing came in — sweeps and matured bills counted as new money.</t>
+          <t>A COMPLETE LIST OF WHAT EVERY BROKER'S WORDS MEAN. Each broker uses its own word for each kind of event, and when we meet a word we do not know, the app currently guesses: money coming in must be a deposit. On the founder's real Vanguard file that guess produced $1,064,493 of deposits into an account where nothing was paid in — the same $220,000 of Treasury bills, rolled three times, counted as brand-new money on every roll.</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1082,7 @@
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
-          <t>The same taxonomy, plus the decision this row's trap names: are fees, tax withheld and margin interest withdrawals? We have not decided once and enforced it. Today reinvestment lines (negative) book as withdrawals — $424,818 of them on the founder's file.</t>
+          <t>The same complete list of broker words — and one decision from you. When a fee is charged, or tax is withheld, money leaves the account, but you did not take it out. Is that a withdrawal? Right now we have never decided, so different parts of the app can disagree. Today Vanguard's reinvestment lines (which are negative amounts) are counted as you taking money out.</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1134,7 @@
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>The household netting rule this row warns about. We do net internal transfers when BOTH accounts are in the measured set, but that set is per-screen and not household-wide.</t>
+          <t>Money moved between two of YOUR OWN accounts must cancel out, or it looks like you both paid in and took out. We do cancel it — but only when both accounts are shown on the same screen. Move money from an account on one screen to an account on another and it counts twice.</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1250,7 @@
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
-          <t>Nothing structural. FIFO from the ledger, sales with no recorded buy counted separately and reported rather than priced. Depends on the ledger being right.</t>
+          <t>Nothing new. Oldest shares are sold first, and a sale with no recorded purchase is reported separately rather than being given a made-up cost. It is only ever as right as the record of your buys and sells.</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1302,7 @@
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>THE COST-BASIS PROVENANCE TAG this file's Gaps tab recommends. Both live brokers sent empty tax lots, so we build ONE synthetic lot from the average price — a different number from a fee-inclusive lot basis, and we do not currently say which we hold.</t>
+          <t>A LABEL SAYING WHERE 'WHAT YOU PAID' CAME FROM. There are three different ways to work it out and they give three different numbers: the true cost of each batch of shares including fees; an average that includes commission; or simply price × shares with fees ignored. Both brokers we connect to send us nothing, so we use the weakest of the three — and the screen does not say so.</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1402,7 @@
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>Not built and probably should not be — Modified Dietz below is strictly better and needs only the flow dates we already store.</t>
+          <t>Not built, and probably should not be. The version below it is better and needs nothing extra.</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1450,7 @@
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
-          <t>BUILD THIS. It is the honest short-window number, needs only BMV plus dated flows, and both are within reach once the snapshot store exists. Today the app shows a simple return instead, which this file correctly calls wrong whenever money moved.</t>
+          <t>BUILD THIS — it is the fair way to measure a short period when money moved in or out. It needs two things: what the account was worth at the start, and the dates money moved. We have the dates. We do not keep a starting value per account, which is the same missing piece that breaks three other rows in this sheet.</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1550,7 @@
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
-          <t>Nothing to build — it solves by bisection, is deterministic, and refuses in four separate ways rather than guessing. It needs the LEDGER to be right: phantom deposits do not make it refuse, they make it answer confidently and wrongly.</t>
+          <t>Nothing to build. It works by trying a rate, seeing if it fits, and narrowing down — always the same answer for the same inputs. It refuses to answer in four situations rather than guessing. But it trusts the record of your deposits completely: a deposit that never happened does not make it refuse, it makes it answer confidently and wrongly.</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1602,7 @@
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>It excludes distributions received — so it is gain-over-cost, not true cumulative return. Add dividends per holding, which we already have in the ledger, and label the lookback limit.</t>
+          <t>It leaves out the dividends you were paid, so it is really 'gain against what I paid', not your full return. We already have the dividends recorded — they just are not added in. It should also say how far back the broker's history actually goes.</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1718,7 @@
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
-          <t>SIGN PRESERVATION. We store every amount as an absolute value at import, so a credit and its offsetting debit both add. That is the founder's $2,387 of interest against $1,193 actually paid.</t>
+          <t>MINUS SIGNS THAT SURVIVE. When a transaction arrives we throw away whether it was money in or money out and keep only the size. So a payment and its matching reversal both add up instead of cancelling. That is why the app showed $2,387 of interest when $1,193 was actually paid — exactly double, because each monthly payment arrives as a pair.</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1770,7 @@
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
-          <t>The reinvestment split this row's trap names, and the same sign fix. A reinvested dividend is income AND a purchase; we must count the income once and the purchase as internal.</t>
+          <t>The same minus-sign fix, plus one rule: when a dividend is automatically reinvested it arrives as two lines — the money paid to you, and the same money buying more shares. It is income ONCE, and the buying half is not new money.</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1922,7 @@
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
-          <t>The price convention this row names — clean vs dirty — recorded alongside the number. We do not state which we assume.</t>
+          <t>One line stating whether the bond's price already includes interest that has built up since the last payment. The same bond has two different 'prices' depending on that, and the yield changes with it. We do not currently say which we used.</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1986,7 @@
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
-          <t>Nothing. Cash classification decides the denominator and our cash-means-cash rule settles it.</t>
+          <t>Nothing. What counts as cash decides what we divide by, and our rule — cash means cash only — settles it.</t>
         </is>
       </c>
     </row>
@@ -1992,7 +2038,7 @@
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>The T-minus-N snapshot again. We weight by CURRENT value, not beginning value, so a holding bought mid-period gets a full-period weight.</t>
+          <t>WHAT THE ACCOUNT WAS WORTH AT THE START of the period. We use today's value instead, so a holding bought halfway through gets credited as though you had owned it the whole time.</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2090,7 @@
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
-          <t>The TARGET half. We show actual allocation with no target to drift from, so 'drift' cannot be computed at all. A product decision before an engineering one.</t>
+          <t>SOMETHING TO DRIFT FROM. We show what you actually hold, but you have never told the app what you are AIMING to hold — so there is no target, and 'drift' cannot be worked out at all. That is a product decision before it is a coding one.</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2194,22 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
           <t>NET WORTH SCREEN — metrics the research file does not cover</t>
         </is>
       </c>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="20" t="n"/>
+      <c r="J35" s="21" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
@@ -2411,7 +2467,7 @@
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>One classifier instead of three. A gold fund, a spot-bitcoin ETF and an option class differently depending on whether the holding arrived by file or by connection.</t>
+          <t>ONE PIECE OF CODE DECIDING WHAT A HOLDING IS, INSTEAD OF THREE. There are three separate places that answer 'what kind of thing is this?' — one for a file you upload, one for a connected broker, one for a whole account — and they were written at different times with different rules. So the SAME holding gets different answers depending how it arrived: a gold fund, a bitcoin fund and an option all count as Alternatives when uploaded from a file, but as ordinary shares when the same holding comes through the broker. Your gold could sit in a different slice of the pie chart purely because of how it got in. Fix: keep the cleverest one, delete the other two, have all three doors use it.</t>
         </is>
       </c>
     </row>
@@ -2525,6 +2581,15 @@
           <t>ACCOUNT DETAIL SCREEN</t>
         </is>
       </c>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20" t="n"/>
+      <c r="I43" s="20" t="n"/>
+      <c r="J43" s="21" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
@@ -2792,6 +2857,15 @@
           <t>HOLDING DETAIL SCREEN</t>
         </is>
       </c>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
+      <c r="H49" s="20" t="n"/>
+      <c r="I49" s="20" t="n"/>
+      <c r="J49" s="21" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
@@ -2893,7 +2967,7 @@
       </c>
       <c r="J51" s="15" t="inlineStr">
         <is>
-          <t>The provenance tag: which of the three definitions this number is. We hold derived-price×units and do not say so.</t>
+          <t>The same label described two rows above — a note saying which of the three ways of working out 'what you paid' this number came from, so nobody compares two figures that were never the same measure.</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3071,7 @@
       </c>
       <c r="J53" s="15" t="inlineStr">
         <is>
-          <t>Real lot dates. Both live brokers sent none, so one synthetic lot carries one date — an unreadable date is treated as SHORT term, the cautious side.</t>
+          <t>THE REAL PURCHASE DATES. Whether a gain is taxed at the lower long-term rate depends on owning something for twelve whole months, judged per batch of shares. Both brokers send us no purchase history at all, so we build a single stand-in batch with one date. Where a date cannot be read we assume short-term, which is the cautious side — understating a tax bill is the worse mistake.</t>
         </is>
       </c>
     </row>
@@ -3215,6 +3289,15 @@
           <t>PERFORMANCE SCREEN</t>
         </is>
       </c>
+      <c r="B58" s="20" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="20" t="n"/>
+      <c r="E58" s="20" t="n"/>
+      <c r="F58" s="20" t="n"/>
+      <c r="G58" s="20" t="n"/>
+      <c r="H58" s="20" t="n"/>
+      <c r="I58" s="20" t="n"/>
+      <c r="J58" s="21" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
@@ -3264,7 +3347,7 @@
       </c>
       <c r="J59" s="15" t="inlineStr">
         <is>
-          <t>An arbitrary date range. It answers six named periods only, so it can never sit beside a statement window — though the engine that takes any two dates already exists, exported and unused.</t>
+          <t>THE ABILITY TO ASK FOR ANY DATE RANGE. It only answers six fixed periods (1 month, 3 months, and so on), so it can never be lined up against the dates on your statement. The code that accepts any two dates is already written and finished — nothing in the app calls it.</t>
         </is>
       </c>
     </row>

--- a/Calculation Module/investment-api-performance-crosswalk.xlsx
+++ b/Calculation Module/investment-api-performance-crosswalk.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="33600" windowHeight="19860" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="33600" windowHeight="19860" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="0. Read Me" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,17 +76,31 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="10"/>
+      <color rgb="007A2E2E"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -110,7 +124,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE3E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF6E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A2E2E"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,18 +162,8 @@
         <fgColor rgb="00EAF3EC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF6E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E2EC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -159,6 +188,65 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="00DDDDDD"/>
       </left>
       <right style="thin">
@@ -171,55 +259,11 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -264,6 +308,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -636,11 +693,11 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="118" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" style="20" min="1" max="1"/>
+    <col width="118" customWidth="1" style="20" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" customHeight="1">
+    <row r="1" ht="19" customHeight="1" s="20">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Performance Metrics x API Field Naming Crosswalk</t>
@@ -654,7 +711,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="58" customHeight="1">
+    <row r="4" ht="58" customHeight="1" s="20">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Purpose</t>
@@ -666,7 +723,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="58" customHeight="1">
+    <row r="5" ht="58" customHeight="1" s="20">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Core finding</t>
@@ -678,7 +735,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
+    <row r="6" ht="58" customHeight="1" s="20">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Second finding</t>
@@ -690,7 +747,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
+    <row r="7" ht="58" customHeight="1" s="20">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Sheet 1</t>
@@ -702,7 +759,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="58" customHeight="1">
+    <row r="8" ht="58" customHeight="1" s="20">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Sheet 2</t>
@@ -714,7 +771,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
+    <row r="9" ht="58" customHeight="1" s="20">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Sheet 3</t>
@@ -726,7 +783,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
+    <row r="10" ht="58" customHeight="1" s="20">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Sheet 4</t>
@@ -738,7 +795,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="58" customHeight="1">
+    <row r="11" ht="58" customHeight="1" s="20">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Confidence</t>
@@ -750,7 +807,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
+    <row r="12" ht="58" customHeight="1" s="20">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Sources read</t>
@@ -762,7 +819,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
+    <row r="13" ht="58" customHeight="1" s="20">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Sheet 5</t>
@@ -785,36 +842,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" style="20" min="1" max="1"/>
+    <col width="17" customWidth="1" style="20" min="2" max="2"/>
+    <col width="44" customWidth="1" style="20" min="3" max="3"/>
+    <col width="26" customWidth="1" style="20" min="4" max="4"/>
+    <col width="22" customWidth="1" style="20" min="5" max="5"/>
+    <col width="62" customWidth="1" style="20" min="6" max="6"/>
+    <col width="26" customWidth="1" style="20" min="7" max="8"/>
+    <col width="16" customWidth="1" style="20" min="9" max="9"/>
+    <col width="62" customWidth="1" style="20" min="10" max="10"/>
+    <col width="66" customWidth="1" style="20" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
+    <row r="1" ht="17" customHeight="1" s="20">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Performance metrics - what you can compute and what it costs you</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="130" customHeight="1" s="20">
       <c r="A2" s="13" t="inlineStr">
         <is>
           <t>'DERIVED' = the standard carries the inputs but not the metric. 'NO' = you must build and persist state the API will never send you.  ||  EXTENDED 2026-08-18: columns G–J and every CREAM row were added by Claude Code, mapping this research onto MoneyKeel's actual screens. Column J is the work list. Original research rows and their wording are unchanged.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="3">
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>RED = the formula in column C is WRONG or incomplete as written, and this cell says what it should be. GREEN = the formula stands; any problem is in the inputs (column J), not the arithmetic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" s="20">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Metric</t>
@@ -865,8 +929,13 @@
           <t>WHAT WE NEED to trust this number</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
+      <c r="K4" s="22" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION — is the formula itself right, and if not what should it be?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1" s="20">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>PERIOD FRAMING (your 10-day window)</t>
@@ -878,7 +947,7 @@
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="56" customHeight="1" s="20">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Beginning market value (BMV)</t>
@@ -929,8 +998,13 @@
           <t>A STORED DAILY PER-ACCOUNT SNAPSHOT. We keep only one number a day for total net worth, so a beginning value per account cannot be read and is back-solved instead — which is how the founder's Vanguard beginning value came out NEGATIVE (−$448,028 against a statement's $378,022). This one gap blocks BMV, contribution-to-return, and any statement reconciliation.</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>FORMULA IS FINE; IT IS UNOBTAINABLE AS WRITTEN. 'Sum of position market values as of T-10' assumes a stored history nobody has. DO NOT let the app back-solve it (BMV = EMV − flows − gain): that is circular and it inherits every ledger error, which is exactly how our beginning value came out at MINUS $448,028 against a statement's $378,022. RECOMMENDATION: store a daily per-account snapshot from first connection, and where no snapshot exists show NO beginning value and no return that depends on one. Absent beats invented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" s="20">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Ending market value (EMV)</t>
@@ -981,8 +1055,13 @@
           <t>Nothing — this is the one figure that already reconciles to the statement to the cent. Keep the as-of timestamp visible so a stale price cannot masquerade as a move.</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" s="20">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Contributions (gross in)</t>
@@ -1020,7 +1099,7 @@
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>PERSONAL_FLOWS / TRANSLATE_BROKER_WORD</t>
+          <t>PERSONAL_FLOWS / INGEST_ACTIVITY_TYPE</t>
         </is>
       </c>
       <c r="I8" s="16" t="inlineStr">
@@ -1030,11 +1109,16 @@
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>A COMPLETE LIST OF WHAT EVERY BROKER'S WORDS MEAN. Each broker uses its own word for each kind of event, and when we meet a word we do not know, the app currently guesses: money coming in must be a deposit. On the founder's real Vanguard file that guess produced $1,064,493 of deposits into an account where nothing was paid in — the same $220,000 of Treasury bills, rolled three times, counted as brand-new money on every roll.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
+          <t>A CLOSED TRANSACTION TAXONOMY. Any broker word we do not recognise is currently guessed from the sign of the amount. On the founder's real file that produced $1,064,493 of contributions on an account where nothing came in — sweeps and matured bills counted as new money.</t>
+        </is>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>FORMULA INCOMPLETE AS WRITTEN. 'Sum of external cash/securities in' is right in principle but does not say what makes something external, which is where all the damage happens. RECOMMENDATION: state it as a rule over a CLOSED list of event types — external money in ONLY, never inferred from the sign of an amount, and an unrecognised word counts in nothing and is shown to the person. A reinvested dividend, a sweep between an account's own sub-balances, and a matured bond paying out are all INTERNAL and none is a contribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1" s="20">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Withdrawals (gross out)</t>
@@ -1082,11 +1166,16 @@
       </c>
       <c r="J9" s="15" t="inlineStr">
         <is>
-          <t>The same complete list of broker words — and one decision from you. When a fee is charged, or tax is withheld, money leaves the account, but you did not take it out. Is that a withdrawal? Right now we have never decided, so different parts of the app can disagree. Today Vanguard's reinvestment lines (which are negative amounts) are counted as you taking money out.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
+          <t>The same taxonomy, plus the decision this row's trap names: are fees, tax withheld and margin interest withdrawals? We have not decided once and enforced it. Today reinvestment lines (negative) book as withdrawals — $424,818 of them on the founder's file.</t>
+        </is>
+      </c>
+      <c r="K9" s="23" t="inlineStr">
+        <is>
+          <t>SAME INCOMPLETENESS, plus the decision this row's own trap names. RECOMMENDATION: define a withdrawal as money leaving the person's control, and classify fees, tax withheld and margin interest as COSTS on their own line — value leaves, but it is not money they took out. Enforce it in one place so no screen can disagree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" s="20">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Net cash flow (NCF)</t>
@@ -1134,7 +1223,12 @@
       </c>
       <c r="J10" s="15" t="inlineStr">
         <is>
-          <t>Money moved between two of YOUR OWN accounts must cancel out, or it looks like you both paid in and took out. We do cancel it — but only when both accounts are shown on the same screen. Move money from an account on one screen to an account on another and it counts twice.</t>
+          <t>The household netting rule this row warns about. We do net internal transfers when BOTH accounts are in the measured set, but that set is per-screen and not household-wide.</t>
+        </is>
+      </c>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS. One addition: netting internal transfers must be evaluated across EVERY account the person holds, not per screen, or a transfer between two of their own accounts double-counts.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1244,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="28" customHeight="1" s="20">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Wealth generated (net gain/loss)</t>
@@ -1201,8 +1295,13 @@
           <t>Everything above it. It is EMV − BMV − NCF, so a wrong BMV and wrong flows land here — and it is shown to the person LABELLED as market movement, which it never measured.</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>THE ARITHMETIC IS RIGHT AND THE LABEL IS WRONG — this is the flawed assumption the founder means. EMV − BMV − NCF is a correct identity, but what it produces is a RESIDUAL: whatever is left after everything else is accounted for. Our app prints it as 'change in investment value', which claims it measured a market movement. It measured nothing. Every error anywhere else in the ledger lands here wearing that label — with nothing moved, a $500 phantom deposit becomes a $500 'market loss', indistinguishable from a real one. RECOMMENDATION: split it in two. Show market movement ONLY where it was measured from actual prices, and show the remainder on its own line as 'we could not account for $X'. A person can act on 'unexplained'; nobody can act on a loss that never happened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" s="20">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Realized gain/loss</t>
@@ -1250,11 +1349,16 @@
       </c>
       <c r="J13" s="15" t="inlineStr">
         <is>
-          <t>Nothing new. Oldest shares are sold first, and a sale with no recorded purchase is reported separately rather than being given a made-up cost. It is only ever as right as the record of your buys and sells.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
+          <t>Nothing structural. FIFO from the ledger, sales with no recorded buy counted separately and reported rather than priced. Depends on the ledger being right.</t>
+        </is>
+      </c>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS. RECOMMENDATION: keep the rule that a sale with no recorded purchase is reported separately rather than assigned a made-up cost — a made-up zero cost reports the whole sale as profit and taxes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" s="20">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Unrealized gain/loss</t>
@@ -1302,11 +1406,16 @@
       </c>
       <c r="J14" s="15" t="inlineStr">
         <is>
-          <t>A LABEL SAYING WHERE 'WHAT YOU PAID' CAME FROM. There are three different ways to work it out and they give three different numbers: the true cost of each batch of shares including fees; an average that includes commission; or simply price × shares with fees ignored. Both brokers we connect to send us nothing, so we use the weakest of the three — and the screen does not say so.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>THE COST-BASIS PROVENANCE TAG this file's Gaps tab recommends. Both live brokers sent empty tax lots, so we build ONE synthetic lot from the average price — a different number from a fee-inclusive lot basis, and we do not currently say which we hold.</t>
+        </is>
+      </c>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS. The risk is that 'cost basis' means three different things across providers. RECOMMENDATION: store which definition each number came from and never compare two that differ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="20">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Simple return</t>
@@ -1357,8 +1466,13 @@
           <t>This row's own trap, which we are living: it is only valid when net flow is zero, and our version measures from whatever day the app was first opened rather than a date the person chose.</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
+      <c r="K15" s="23" t="inlineStr">
+        <is>
+          <t>FORMULA IS CORRECT BUT MUST NOT BE USED HERE, and this row already says so: it is valid only when net flow is zero. RECOMMENDATION: do not show it for any window where money moved. Our version compounds the problem by measuring from whatever day the app was installed rather than a date the person chose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1" s="20">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Simple Dietz</t>
@@ -1394,7 +1508,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr"/>
+      <c r="H16" s="15" t="n"/>
       <c r="I16" s="18" t="inlineStr">
         <is>
           <t>NOT BUILT</t>
@@ -1402,11 +1516,16 @@
       </c>
       <c r="J16" s="15" t="inlineStr">
         <is>
-          <t>Not built, and probably should not be. The version below it is better and needs nothing extra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
+          <t>Not built and probably should not be — Modified Dietz below is strictly better and needs only the flow dates we already store.</t>
+        </is>
+      </c>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1" s="20">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Modified Dietz (money-weighted)</t>
@@ -1442,7 +1561,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr"/>
+      <c r="H17" s="15" t="n"/>
       <c r="I17" s="18" t="inlineStr">
         <is>
           <t>NOT BUILT</t>
@@ -1450,11 +1569,16 @@
       </c>
       <c r="J17" s="15" t="inlineStr">
         <is>
-          <t>BUILD THIS — it is the fair way to measure a short period when money moved in or out. It needs two things: what the account was worth at the start, and the dates money moved. We have the dates. We do not keep a starting value per account, which is the same missing piece that breaks three other rows in this sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
+          <t>BUILD THIS. It is the honest short-window number, needs only BMV plus dated flows, and both are within reach once the snapshot store exists. Today the app shows a simple return instead, which this file correctly calls wrong whenever money moved.</t>
+        </is>
+      </c>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>THE RIGHT DEFAULT FOR SHORT WINDOWS, and it is the formula we should adopt. It needs only a beginning value and dated flows. RECOMMENDATION: make this the headline period return once the snapshot store exists, and keep IRR as the 'your personal return' figure alongside it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1" s="20">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Daily TWR (chain-linked)</t>
@@ -1490,7 +1614,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr"/>
+      <c r="H18" s="15" t="n"/>
       <c r="I18" s="18" t="inlineStr">
         <is>
           <t>NOT BUILT</t>
@@ -1501,8 +1625,13 @@
           <t>The daily valuation series. Same blocker as BMV: no daily per-account store. Worth naming as the eventual target, not the next step.</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1" s="20">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>IRR / money-weighted return (XIRR)</t>
@@ -1550,11 +1679,16 @@
       </c>
       <c r="J19" s="15" t="inlineStr">
         <is>
-          <t>Nothing to build. It works by trying a rate, seeing if it fits, and narrowing down — always the same answer for the same inputs. It refuses to answer in four situations rather than guessing. But it trusts the record of your deposits completely: a deposit that never happened does not make it refuse, it makes it answer confidently and wrongly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
+          <t>Nothing to build — it solves by bisection, is deterministic, and refuses in four separate ways rather than guessing. It needs the LEDGER to be right: phantom deposits do not make it refuse, they make it answer confidently and wrongly.</t>
+        </is>
+      </c>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS and our implementation is sound. RECOMMENDATION: keep the rule that it is NOT annualised for short windows — this row's trap is real, and annualising ten days produces absurd figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1" s="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Cumulative return since inception</t>
@@ -1602,11 +1736,16 @@
       </c>
       <c r="J20" s="15" t="inlineStr">
         <is>
-          <t>It leaves out the dividends you were paid, so it is really 'gain against what I paid', not your full return. We already have the dividends recorded — they just are not added in. It should also say how far back the broker's history actually goes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>It excludes distributions received — so it is gain-over-cost, not true cumulative return. Add dividends per holding, which we already have in the ledger, and label the lookback limit.</t>
+        </is>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>FORMULA AS WRITTEN IS RIGHT; OUR IMPLEMENTATION IS NOT. Ours omits distributions received, so it is gain-over-cost rather than a cumulative return. RECOMMENDATION: add income per holding, which the ledger already carries, and state the lookback limit beside it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1" s="20">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Annualized / CAGR</t>
@@ -1655,6 +1794,11 @@
       <c r="J21" s="15" t="inlineStr">
         <is>
           <t>Nothing. We annualise only the 3-year figure, which matches this row's guidance.</t>
+        </is>
+      </c>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1814,7 @@
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="42" customHeight="1" s="20">
       <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Interest income (period)</t>
@@ -1718,11 +1862,16 @@
       </c>
       <c r="J23" s="15" t="inlineStr">
         <is>
-          <t>MINUS SIGNS THAT SURVIVE. When a transaction arrives we throw away whether it was money in or money out and keep only the size. So a payment and its matching reversal both add up instead of cancelling. That is why the app showed $2,387 of interest when $1,193 was actually paid — exactly double, because each monthly payment arrives as a pair.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
+          <t>SIGN PRESERVATION. We store every amount as an absolute value at import, so a credit and its offsetting debit both add. That is the founder's $2,387 of interest against $1,193 actually paid.</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS; THE SUMMING IS WRONG. Summing 'interest transactions' must use SIGNED amounts. We discard the sign when a transaction is imported, so a payment and its reversal both add — which is why the app showed $2,387 against $1,193 actually received. RECOMMENDATION: preserve the sign at import, and carry direction in its own field the way the FDX standard does rather than inferring it from the number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1" s="20">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Dividend income (period)</t>
@@ -1770,11 +1919,16 @@
       </c>
       <c r="J24" s="15" t="inlineStr">
         <is>
-          <t>The same minus-sign fix, plus one rule: when a dividend is automatically reinvested it arrives as two lines — the money paid to you, and the same money buying more shares. It is income ONCE, and the buying half is not new money.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
+          <t>The reinvestment split this row's trap names, and the same sign fix. A reinvested dividend is income AND a purchase; we must count the income once and the purchase as internal.</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>FORMULA NEEDS ONE MORE RULE. RECOMMENDATION: count a reinvested dividend as income ONCE and treat the matching purchase as internal. Never let either leg touch contributions. Show cash and reinvested separately — they mean different things to a retiree living off income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1" s="20">
       <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Accrued interest / accrued income</t>
@@ -1810,7 +1964,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="15" t="inlineStr"/>
+      <c r="H25" s="15" t="n"/>
       <c r="I25" s="18" t="inlineStr">
         <is>
           <t>NOT BUILT</t>
@@ -1821,8 +1975,13 @@
           <t>A FIELD TO PUT IT IN. Vanguard's file HAS an 'Accrued Interest' column — $1,289.40 on the founder's T-note purchase — and we capture it nowhere, so it silently inflates that buy's cost.</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
+      <c r="K25" s="23" t="inlineStr">
+        <is>
+          <t>NOT A DERIVED METRIC AND SHOULD NOT BE TREATED AS ONE. RECOMMENDATION: capture the accrual where a source provides it — Vanguard's file has an 'Accrued Interest' column, $1,289.40 on one real purchase — and hold it apart from cost basis, which it currently inflates silently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1" s="20">
       <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Current yield (bond)</t>
@@ -1873,8 +2032,13 @@
           <t>The coupon, which this row says no standard supplies. We parse it out of the description text. That is correct and should be documented as permanent, not temporary.</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS: annual coupon ÷ current price, where the coupon is paid on FACE value and the price is what it is worth today. RECOMMENDATION: confirming the coupon must come from the description text is permanent, not temporary — verified in FDX 6.3 and 6.4 that no standard carries it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1" s="20">
       <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Yield to maturity</t>
@@ -1922,7 +2086,12 @@
       </c>
       <c r="J27" s="15" t="inlineStr">
         <is>
-          <t>One line stating whether the bond's price already includes interest that has built up since the last payment. The same bond has two different 'prices' depending on that, and the yield changes with it. We do not currently say which we used.</t>
+          <t>The price convention this row names — clean vs dirty — recorded alongside the number. We do not state which we assume.</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS. RECOMMENDATION: record whether the price used already includes interest built up since the last payment. The same bond has two prices and two yields depending on that, and we do not currently say which.</t>
         </is>
       </c>
     </row>
@@ -1938,7 +2107,7 @@
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="9" t="n"/>
     </row>
-    <row r="29" ht="28" customHeight="1">
+    <row r="29" ht="28" customHeight="1" s="20">
       <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Position weight</t>
@@ -1986,11 +2155,16 @@
       </c>
       <c r="J29" s="15" t="inlineStr">
         <is>
-          <t>Nothing. What counts as cash decides what we divide by, and our rule — cash means cash only — settles it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
+          <t>Nothing. Cash classification decides the denominator and our cash-means-cash rule settles it.</t>
+        </is>
+      </c>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" s="20">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Contribution to return</t>
@@ -2038,11 +2212,16 @@
       </c>
       <c r="J30" s="15" t="inlineStr">
         <is>
-          <t>WHAT THE ACCOUNT WAS WORTH AT THE START of the period. We use today's value instead, so a holding bought halfway through gets credited as though you had owned it the whole time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
+          <t>The T-minus-N snapshot again. We weight by CURRENT value, not beginning value, so a holding bought mid-period gets a full-period weight.</t>
+        </is>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>FORMULA AS WRITTEN IS RIGHT — 'weight AT BMV' — and our implementation ignores that. We weight by today's value, so a holding bought halfway through the period is credited as if held throughout. RECOMMENDATION: implement it exactly as this row states, once beginning values exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1" s="20">
       <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Allocation and drift</t>
@@ -2090,11 +2269,16 @@
       </c>
       <c r="J31" s="15" t="inlineStr">
         <is>
-          <t>SOMETHING TO DRIFT FROM. We show what you actually hold, but you have never told the app what you are AIMING to hold — so there is no target, and 'drift' cannot be worked out at all. That is a product decision before it is a coding one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
+          <t>The TARGET half. We show actual allocation with no target to drift from, so 'drift' cannot be computed at all. A product decision before an engineering one.</t>
+        </is>
+      </c>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS but half its inputs do not exist for us: there is no target allocation, so drift cannot be computed. RECOMMENDATION: either capture a target, or show allocation only and stop using the word drift.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" s="20">
       <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Benchmark-relative return</t>
@@ -2145,8 +2329,13 @@
           <t>Nothing — market data is ours, as this row says it must be. The benchmark CHOICE per account type is our judgement and should be stated on screen.</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" s="20">
       <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Fees drag</t>
@@ -2182,7 +2371,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H33" s="15" t="inlineStr"/>
+      <c r="H33" s="15" t="n"/>
       <c r="I33" s="18" t="inlineStr">
         <is>
           <t>NOT BUILT</t>
@@ -2191,6 +2380,11 @@
       <c r="J33" s="15" t="inlineStr">
         <is>
           <t>A FEES LINE AT ALL. The change walk has no fees row, so the $460 of ADR custody fees on the founder's file land inside 'change in investment value' with nowhere else to go.</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS. RECOMMENDATION: it cannot be computed until fees have a line of their own; today they fall into the residual and are reported as investment performance.</t>
         </is>
       </c>
     </row>
@@ -2201,17 +2395,17 @@
           <t>NET WORTH SCREEN — metrics the research file does not cover</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n"/>
-      <c r="C35" s="20" t="n"/>
-      <c r="D35" s="20" t="n"/>
-      <c r="E35" s="20" t="n"/>
-      <c r="F35" s="20" t="n"/>
-      <c r="G35" s="20" t="n"/>
-      <c r="H35" s="20" t="n"/>
-      <c r="I35" s="20" t="n"/>
-      <c r="J35" s="21" t="n"/>
-    </row>
-    <row r="36">
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="25" t="n"/>
+      <c r="D35" s="25" t="n"/>
+      <c r="E35" s="25" t="n"/>
+      <c r="F35" s="25" t="n"/>
+      <c r="G35" s="25" t="n"/>
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="25" t="n"/>
+      <c r="J35" s="26" t="n"/>
+    </row>
+    <row r="36" ht="32" customHeight="1" s="20">
       <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Net worth</t>
@@ -2262,8 +2456,13 @@
           <t>Nothing. Computed, never stored independently.</t>
         </is>
       </c>
-    </row>
-    <row r="37">
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1" s="20">
       <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Total cash</t>
@@ -2314,8 +2513,13 @@
           <t>The contradiction closed: the class rule says a money-market fund is measured, while the on-screen grouping table still marks it Cash. Founder finding F6, still open.</t>
         </is>
       </c>
-    </row>
-    <row r="38">
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1" s="20">
       <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Total investments</t>
@@ -2366,8 +2570,13 @@
           <t>Nothing.</t>
         </is>
       </c>
-    </row>
-    <row r="39">
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1" s="20">
       <c r="A39" s="18" t="inlineStr">
         <is>
           <t>Investable assets</t>
@@ -2418,8 +2627,13 @@
           <t>Nothing.</t>
         </is>
       </c>
-    </row>
-    <row r="40">
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1" s="20">
       <c r="A40" s="18" t="inlineStr">
         <is>
           <t>Asset allocation by class</t>
@@ -2467,11 +2681,16 @@
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>ONE PIECE OF CODE DECIDING WHAT A HOLDING IS, INSTEAD OF THREE. There are three separate places that answer 'what kind of thing is this?' — one for a file you upload, one for a connected broker, one for a whole account — and they were written at different times with different rules. So the SAME holding gets different answers depending how it arrived: a gold fund, a bitcoin fund and an option all count as Alternatives when uploaded from a file, but as ordinary shares when the same holding comes through the broker. Your gold could sit in a different slice of the pie chart purely because of how it got in. Fix: keep the cleverest one, delete the other two, have all three doors use it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+          <t>One classifier instead of three. A gold fund, a spot-bitcoin ETF and an option class differently depending on whether the holding arrived by file or by connection.</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS. RECOMMENDATION: one piece of code deciding what a holding is, used by all three doors, so the same holding cannot land in different slices depending on how it arrived.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1" s="20">
       <c r="A41" s="18" t="inlineStr">
         <is>
           <t>Retirement pot (nest egg)</t>
@@ -2522,8 +2741,13 @@
           <t>Nothing.</t>
         </is>
       </c>
-    </row>
-    <row r="42">
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1" s="20">
       <c r="A42" s="18" t="inlineStr">
         <is>
           <t>Net worth trend series</t>
@@ -2572,6 +2796,11 @@
       <c r="J42" s="15" t="inlineStr">
         <is>
           <t>Per-account daily values, and a stated retention. Today it is one total per day, pruned at 400 days, so 'since I started' and '5 years' are permanently unanswerable and nothing on screen says so.</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>NOT A FORMULA PROBLEM — A HONESTY PROBLEM. RECOMMENDATION: label every change figure with the date it is actually measured FROM, so a figure measured from install day says so. And state the retention limit rather than letting older history disappear silently.</t>
         </is>
       </c>
     </row>
@@ -2581,17 +2810,17 @@
           <t>ACCOUNT DETAIL SCREEN</t>
         </is>
       </c>
-      <c r="B43" s="20" t="n"/>
-      <c r="C43" s="20" t="n"/>
-      <c r="D43" s="20" t="n"/>
-      <c r="E43" s="20" t="n"/>
-      <c r="F43" s="20" t="n"/>
-      <c r="G43" s="20" t="n"/>
-      <c r="H43" s="20" t="n"/>
-      <c r="I43" s="20" t="n"/>
-      <c r="J43" s="21" t="n"/>
-    </row>
-    <row r="44">
+      <c r="B43" s="25" t="n"/>
+      <c r="C43" s="25" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="25" t="n"/>
+      <c r="G43" s="25" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="25" t="n"/>
+      <c r="J43" s="26" t="n"/>
+    </row>
+    <row r="44" ht="32" customHeight="1" s="20">
       <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Account value + freshness</t>
@@ -2642,8 +2871,13 @@
           <t>Nothing. Six months is the staleness line for a typed value; a live-priced account is exempt.</t>
         </is>
       </c>
-    </row>
-    <row r="45">
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1" s="20">
       <c r="A45" s="18" t="inlineStr">
         <is>
           <t>Uninvested cash in an account</t>
@@ -2694,8 +2928,13 @@
           <t>A founder decision: show the money-market fund as a holding (recommended) or keep it inside cash. Today it is subtracted from cash AND filtered out of holdings, so it is in neither place.</t>
         </is>
       </c>
-    </row>
-    <row r="46">
+      <c r="K45" s="23" t="inlineStr">
+        <is>
+          <t>FORMULA IS RIGHT AND THE SURROUNDING CODE UNDOES IT. We subtract money-market funds from cash AND separately drop them from the holdings list, so the money is in neither place. RECOMMENDATION: subtract once, keep the fund visible as a holding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1" s="20">
       <c r="A46" s="18" t="inlineStr">
         <is>
           <t>One account split across classes</t>
@@ -2746,8 +2985,13 @@
           <t>The WORDS under each slice use a different rule from the amounts, so a slice's value and its description can disagree.</t>
         </is>
       </c>
-    </row>
-    <row r="47">
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1" s="20">
       <c r="A47" s="18" t="inlineStr">
         <is>
           <t>How this account is taxed</t>
@@ -2798,8 +3042,13 @@
           <t>Nothing on SnapTrade — an unrecognised type comes back NOT confident and the app asks. On Plaid, use its documented subtypes and stop asking.</t>
         </is>
       </c>
-    </row>
-    <row r="48">
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1" s="20">
       <c r="A48" s="18" t="inlineStr">
         <is>
           <t>Account activity list</t>
@@ -2848,6 +3097,11 @@
       <c r="J48" s="15" t="inlineStr">
         <is>
           <t>Nothing. Depth is tracked per account and only ever grows.</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
         </is>
       </c>
     </row>
@@ -2857,17 +3111,17 @@
           <t>HOLDING DETAIL SCREEN</t>
         </is>
       </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
-      <c r="G49" s="20" t="n"/>
-      <c r="H49" s="20" t="n"/>
-      <c r="I49" s="20" t="n"/>
-      <c r="J49" s="21" t="n"/>
-    </row>
-    <row r="50">
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="25" t="n"/>
+      <c r="F49" s="25" t="n"/>
+      <c r="G49" s="25" t="n"/>
+      <c r="H49" s="25" t="n"/>
+      <c r="I49" s="25" t="n"/>
+      <c r="J49" s="26" t="n"/>
+    </row>
+    <row r="50" ht="16" customHeight="1" s="20">
       <c r="A50" s="18" t="inlineStr">
         <is>
           <t>Shares held</t>
@@ -2918,8 +3172,13 @@
           <t>Nothing.</t>
         </is>
       </c>
-    </row>
-    <row r="51">
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1" s="20">
       <c r="A51" s="18" t="inlineStr">
         <is>
           <t>Cost basis</t>
@@ -2967,11 +3226,16 @@
       </c>
       <c r="J51" s="15" t="inlineStr">
         <is>
-          <t>The same label described two rows above — a note saying which of the three ways of working out 'what you paid' this number came from, so nobody compares two figures that were never the same measure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
+          <t>The provenance tag: which of the three definitions this number is. We hold derived-price×units and do not say so.</t>
+        </is>
+      </c>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1" s="20">
       <c r="A52" s="18" t="inlineStr">
         <is>
           <t>Market value</t>
@@ -3022,8 +3286,13 @@
           <t>Nothing.</t>
         </is>
       </c>
-    </row>
-    <row r="53">
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1" s="20">
       <c r="A53" s="18" t="inlineStr">
         <is>
           <t>Capital gains split (long vs short)</t>
@@ -3071,11 +3340,16 @@
       </c>
       <c r="J53" s="15" t="inlineStr">
         <is>
-          <t>THE REAL PURCHASE DATES. Whether a gain is taxed at the lower long-term rate depends on owning something for twelve whole months, judged per batch of shares. Both brokers send us no purchase history at all, so we build a single stand-in batch with one date. Where a date cannot be read we assume short-term, which is the cautious side — understating a tax bill is the worse mistake.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
+          <t>Real lot dates. Both live brokers sent none, so one synthetic lot carries one date — an unreadable date is treated as SHORT term, the cautious side.</t>
+        </is>
+      </c>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS — judged per batch of shares on its own purchase date, never per holding. RECOMMENDATION: keep 'unreadable date means short-term'; erring the other way understates a tax bill, which is the worse mistake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1" s="20">
       <c r="A54" s="18" t="inlineStr">
         <is>
           <t>Tax on those gains</t>
@@ -3126,8 +3400,13 @@
           <t>Nothing.</t>
         </is>
       </c>
-    </row>
-    <row r="55">
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1" s="20">
       <c r="A55" s="18" t="inlineStr">
         <is>
           <t>Price history graph</t>
@@ -3178,8 +3457,13 @@
           <t>Confirmation that the graph is suppressed — not flat-lined — for anything without a tradeable ticker.</t>
         </is>
       </c>
-    </row>
-    <row r="56">
+      <c r="K55" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1" s="20">
       <c r="A56" s="18" t="inlineStr">
         <is>
           <t>Bond facts: face, coupon, maturity, yields</t>
@@ -3230,8 +3514,13 @@
           <t>Nothing new — but document the text parser as PERMANENT infrastructure, not a stopgap. It is the same approach the standard itself implies.</t>
         </is>
       </c>
-    </row>
-    <row r="57">
+      <c r="K56" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1" s="20">
       <c r="A57" s="18" t="inlineStr">
         <is>
           <t>Option position detail</t>
@@ -3280,6 +3569,11 @@
       <c r="J57" s="15" t="inlineStr">
         <is>
           <t>Cash-settled exercises. An in-the-money cash settlement carries its money on the row we skip, so real proceeds are dropped.</t>
+        </is>
+      </c>
+      <c r="K57" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
         </is>
       </c>
     </row>
@@ -3289,17 +3583,17 @@
           <t>PERFORMANCE SCREEN</t>
         </is>
       </c>
-      <c r="B58" s="20" t="n"/>
-      <c r="C58" s="20" t="n"/>
-      <c r="D58" s="20" t="n"/>
-      <c r="E58" s="20" t="n"/>
-      <c r="F58" s="20" t="n"/>
-      <c r="G58" s="20" t="n"/>
-      <c r="H58" s="20" t="n"/>
-      <c r="I58" s="20" t="n"/>
-      <c r="J58" s="21" t="n"/>
-    </row>
-    <row r="59">
+      <c r="B58" s="25" t="n"/>
+      <c r="C58" s="25" t="n"/>
+      <c r="D58" s="25" t="n"/>
+      <c r="E58" s="25" t="n"/>
+      <c r="F58" s="25" t="n"/>
+      <c r="G58" s="25" t="n"/>
+      <c r="H58" s="25" t="n"/>
+      <c r="I58" s="25" t="n"/>
+      <c r="J58" s="26" t="n"/>
+    </row>
+    <row r="59" ht="48" customHeight="1" s="20">
       <c r="A59" s="18" t="inlineStr">
         <is>
           <t>Portfolio period return</t>
@@ -3347,11 +3641,16 @@
       </c>
       <c r="J59" s="15" t="inlineStr">
         <is>
-          <t>THE ABILITY TO ASK FOR ANY DATE RANGE. It only answers six fixed periods (1 month, 3 months, and so on), so it can never be lined up against the dates on your statement. The code that accepts any two dates is already written and finished — nothing in the app calls it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
+          <t>An arbitrary date range. It answers six named periods only, so it can never sit beside a statement window — though the engine that takes any two dates already exists, exported and unused.</t>
+        </is>
+      </c>
+      <c r="K59" s="24" t="inlineStr">
+        <is>
+          <t>FORMULA STANDS — money-weighted across holdings, which is correct. RECOMMENDATION: allow any date range, so it can be laid beside a statement. The code that does this already exists and is unused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="16" customHeight="1" s="20">
       <c r="A60" s="18" t="inlineStr">
         <is>
           <t>Winners and detractors</t>
@@ -3402,8 +3701,13 @@
           <t>Beginning-of-period weights, per this file's own row above.</t>
         </is>
       </c>
-    </row>
-    <row r="61">
+      <c r="K60" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="16" customHeight="1" s="20">
       <c r="A61" s="18" t="inlineStr">
         <is>
           <t>Concentration</t>
@@ -3454,8 +3758,13 @@
           <t>Nothing.</t>
         </is>
       </c>
-    </row>
-    <row r="62">
+      <c r="K61" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="48" customHeight="1" s="20">
       <c r="A62" s="18" t="inlineStr">
         <is>
           <t>Portfolio vs benchmark trend</t>
@@ -3506,8 +3815,13 @@
           <t>Share counts AS AT each past date. Every past point uses TODAY'S share count, so a holding bought last week is drawn as held all year. Lot purchase dates are already on the record — a cheap fix.</t>
         </is>
       </c>
-    </row>
-    <row r="63">
+      <c r="K62" s="23" t="inlineStr">
+        <is>
+          <t>FORMULA IS WRONG AS IMPLEMENTED. Valuing every past date with TODAY'S share count draws a history the person never held. RECOMMENDATION: count only the shares owned on or before each point, using purchase dates already on the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1" s="20">
       <c r="A63" s="18" t="inlineStr">
         <is>
           <t>Look back — what if I had moved this money</t>
@@ -3556,6 +3870,11 @@
       <c r="J63" s="15" t="inlineStr">
         <is>
           <t>Nothing.</t>
+        </is>
+      </c>
+      <c r="K63" s="24" t="inlineStr">
+        <is>
+          <t>Formula stands. No change recommended — see column J for anything the inputs still need.</t>
         </is>
       </c>
     </row>
@@ -3579,19 +3898,19 @@
   <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" style="20" min="1" max="1"/>
+    <col width="30" customWidth="1" style="20" min="2" max="2"/>
+    <col width="32" customWidth="1" style="20" min="3" max="3"/>
+    <col width="26" customWidth="1" style="20" min="4" max="4"/>
+    <col width="32" customWidth="1" style="20" min="5" max="5"/>
+    <col width="30" customWidth="1" style="20" min="6" max="6"/>
+    <col width="22" customWidth="1" style="20" min="7" max="7"/>
+    <col width="26" customWidth="1" style="20" min="8" max="8"/>
+    <col width="40" customWidth="1" style="20" min="9" max="9"/>
+    <col width="52" customWidth="1" style="20" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
+    <row r="1" ht="17" customHeight="1" s="20">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Field-name crosswalk by data element</t>
@@ -3605,7 +3924,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="34" customHeight="1" s="20">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Data element</t>
@@ -3673,7 +3992,7 @@
       <c r="I5" s="8" t="n"/>
       <c r="J5" s="9" t="n"/>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="28" customHeight="1" s="20">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Account container</t>
@@ -3725,7 +4044,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="42" customHeight="1" s="20">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Total account value</t>
@@ -3777,7 +4096,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="28" customHeight="1" s="20">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Cash / sweep balance</t>
@@ -3829,7 +4148,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" ht="42" customHeight="1" s="20">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Valuation as-of timestamp</t>
@@ -3881,7 +4200,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="56" customHeight="1" s="20">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Beginning-of-period value</t>
@@ -3933,7 +4252,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="112" customHeight="1">
+    <row r="11" ht="112" customHeight="1" s="20">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Period return / ROI</t>
@@ -4001,7 +4320,7 @@
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="9" t="n"/>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" ht="42" customHeight="1" s="20">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Holding record</t>
@@ -4053,7 +4372,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="28" customHeight="1" s="20">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Security name</t>
@@ -4105,7 +4424,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
+    <row r="15" ht="28" customHeight="1" s="20">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Ticker</t>
@@ -4157,7 +4476,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1">
+    <row r="16" ht="42" customHeight="1" s="20">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>CUSIP / ISIN / SEDOL</t>
@@ -4205,7 +4524,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="70" customHeight="1" s="20">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Asset type</t>
@@ -4257,7 +4576,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
+    <row r="18" ht="28" customHeight="1" s="20">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Quantity</t>
@@ -4309,7 +4628,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
+    <row r="19" ht="28" customHeight="1" s="20">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Current price</t>
@@ -4361,7 +4680,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
+    <row r="20" ht="28" customHeight="1" s="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Market value</t>
@@ -4413,7 +4732,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
+    <row r="21" ht="28" customHeight="1" s="20">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Face value (bonds)</t>
@@ -4465,7 +4784,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="70" customHeight="1">
+    <row r="22" ht="70" customHeight="1" s="20">
       <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Cost basis</t>
@@ -4517,7 +4836,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
+    <row r="23" ht="28" customHeight="1" s="20">
       <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Purchase price / date</t>
@@ -4569,7 +4888,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="56" customHeight="1" s="20">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Long / short</t>
@@ -4616,7 +4935,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
+    <row r="25" ht="28" customHeight="1" s="20">
       <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Cash-equivalent flag</t>
@@ -4668,7 +4987,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
+    <row r="26" ht="28" customHeight="1" s="20">
       <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Coupon rate</t>
@@ -4720,7 +5039,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="56" customHeight="1" s="20">
       <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Maturity date</t>
@@ -4824,7 +5143,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
+    <row r="29" ht="42" customHeight="1" s="20">
       <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Asset classification</t>
@@ -4892,7 +5211,7 @@
       <c r="I30" s="8" t="n"/>
       <c r="J30" s="9" t="n"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="56" customHeight="1" s="20">
       <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Transaction record</t>
@@ -4944,7 +5263,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="84" customHeight="1">
+    <row r="32" ht="84" customHeight="1" s="20">
       <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Transaction type</t>
@@ -4996,7 +5315,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="28" customHeight="1">
+    <row r="33" ht="28" customHeight="1" s="20">
       <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Trade / posted date</t>
@@ -5048,7 +5367,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="56" customHeight="1" s="20">
       <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Units / price / amount</t>
@@ -5100,7 +5419,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
+    <row r="35" ht="28" customHeight="1" s="20">
       <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Fees / commission</t>
@@ -5152,7 +5471,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
+    <row r="36" ht="28" customHeight="1" s="20">
       <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Income type</t>
@@ -5204,7 +5523,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="56" customHeight="1" s="20">
       <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Unrealized gain/loss (P&amp;L)</t>
@@ -5270,16 +5589,16 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" style="20" min="1" max="1"/>
+    <col width="34" customWidth="1" style="20" min="2" max="2"/>
+    <col width="22" customWidth="1" style="20" min="3" max="3"/>
+    <col width="26" customWidth="1" style="20" min="4" max="4"/>
+    <col width="24" customWidth="1" style="20" min="5" max="5"/>
+    <col width="42" customWidth="1" style="20" min="6" max="6"/>
+    <col width="56" customWidth="1" style="20" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
+    <row r="1" ht="17" customHeight="1" s="20">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Per-asset-class fields and semantic traps</t>
@@ -5293,7 +5612,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="34" customHeight="1" s="20">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Asset class</t>
@@ -5330,7 +5649,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="42" customHeight="1" s="20">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Common stock</t>
@@ -5367,7 +5686,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="28" customHeight="1" s="20">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>ETF</t>
@@ -5404,7 +5723,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="28" customHeight="1" s="20">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Mutual fund</t>
@@ -5441,7 +5760,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="42" customHeight="1" s="20">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Money market / cash</t>
@@ -5478,7 +5797,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="84" customHeight="1">
+    <row r="9" ht="84" customHeight="1" s="20">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Bond (corporate, muni, govt, TIPS, MBS, CMO)</t>
@@ -5515,7 +5834,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="28" customHeight="1" s="20">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>CD</t>
@@ -5552,7 +5871,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
+    <row r="11" ht="42" customHeight="1" s="20">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Option</t>
@@ -5589,7 +5908,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" ht="42" customHeight="1" s="20">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Crypto / digital asset</t>
@@ -5626,7 +5945,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" ht="42" customHeight="1" s="20">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Commodity</t>
@@ -5663,7 +5982,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="28" customHeight="1" s="20">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Currency / FX</t>
@@ -5700,7 +6019,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
+    <row r="15" ht="28" customHeight="1" s="20">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Annuity / variable life</t>
@@ -5737,7 +6056,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="56" customHeight="1" s="20">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Equity comp (RSU, RSA, ESO, performance units)</t>
@@ -5788,19 +6107,19 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="82" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" style="20" min="1" max="1"/>
+    <col width="60" customWidth="1" style="20" min="2" max="2"/>
+    <col width="82" customWidth="1" style="20" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
+    <row r="1" ht="17" customHeight="1" s="20">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Gaps, workarounds, and the decisions you must make explicitly</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="34" customHeight="1" s="20">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Gap / decision</t>
@@ -5817,7 +6136,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="28" customHeight="1" s="20">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>No historical valuation in any consumer standard</t>
@@ -5834,7 +6153,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="28" customHeight="1" s="20">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>No performance field anywhere on the consumer rails</t>
@@ -5851,7 +6170,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="42" customHeight="1" s="20">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Transaction taxonomy is the real integration cost</t>
@@ -5868,7 +6187,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="28" customHeight="1" s="20">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Three incompatible cost-basis definitions</t>
@@ -5885,7 +6204,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="28" customHeight="1" s="20">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Bond and fixed-income data is thin in FDX</t>
@@ -5902,7 +6221,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
+    <row r="9" ht="28" customHeight="1" s="20">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Security identity is not stable</t>
@@ -5919,7 +6238,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="28" customHeight="1" s="20">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Asset-type enums do not map cleanly</t>
@@ -5936,7 +6255,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="28" customHeight="1" s="20">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>As-of timestamps are unnormalized and often stale</t>
@@ -5953,7 +6272,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="28" customHeight="1" s="20">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Corporate actions are inconsistently transmitted</t>
@@ -5970,7 +6289,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="28" customHeight="1" s="20">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Fees are partly invisible</t>
@@ -6021,7 +6340,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
+    <row r="16" ht="28" customHeight="1" s="20">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Lookback limits</t>
@@ -6038,7 +6357,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1">
+    <row r="17" ht="42" customHeight="1" s="20">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>1033 landscape</t>
@@ -6069,11 +6388,11 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="74" customWidth="1" min="2" max="3"/>
+    <col width="30" customWidth="1" style="20" min="1" max="1"/>
+    <col width="74" customWidth="1" style="20" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17" customHeight="1">
+    <row r="1" ht="17" customHeight="1" s="20">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>SnapTrade - how it compares to the FDX-family rails</t>
@@ -6087,7 +6406,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="30" customHeight="1" s="20">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Point</t>
@@ -6104,7 +6423,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="28" customHeight="1" s="20">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>WHERE SNAPTRADE IS STRUCTURALLY DIFFERENT</t>
@@ -6113,7 +6432,7 @@
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="42" customHeight="1" s="20">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Not an FDX implementation</t>
@@ -6130,7 +6449,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="42" customHeight="1" s="20">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>It ships P&amp;L</t>
@@ -6147,7 +6466,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="42" customHeight="1" s="20">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>It has a historical value endpoint</t>
@@ -6164,7 +6483,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="56" customHeight="1" s="20">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>It once had a performance API</t>
@@ -6181,7 +6500,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" ht="42" customHeight="1" s="20">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Asset-class coverage is the widest</t>
@@ -6198,7 +6517,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="28" customHeight="1" s="20">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Transaction history is deeper</t>
@@ -6215,7 +6534,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="28" customHeight="1" s="20">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>WHERE IT IS WEAKER THAN THE FDX RAILS</t>
@@ -6224,7 +6543,7 @@
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="9" t="n"/>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="28" customHeight="1" s="20">
       <c r="A13" s="10" t="inlineStr">
         <is>
           <t>No CUSIP or ISIN</t>
@@ -6241,7 +6560,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="28" customHeight="1" s="20">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Fixed income is thin to absent</t>
@@ -6258,7 +6577,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
+    <row r="15" ht="28" customHeight="1" s="20">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>No market value field</t>
@@ -6292,7 +6611,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
+    <row r="17" ht="28" customHeight="1" s="20">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Price freshness is plan-dependent</t>
@@ -6309,7 +6628,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
+    <row r="18" ht="42" customHeight="1" s="20">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Type fallback to raw broker strings</t>
@@ -6343,7 +6662,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
+    <row r="20" ht="28" customHeight="1" s="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>HOW TO POSITION IT IN YOUR STACK</t>
@@ -6352,7 +6671,7 @@
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="9" t="n"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="56" customHeight="1" s="20">
       <c r="A21" s="10" t="inlineStr">
         <is>
           <t>Recommended split</t>
@@ -6369,7 +6688,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="42" customHeight="1" s="20">
       <c r="A22" s="10" t="inlineStr">
         <is>
           <t>What does not change</t>
